--- a/מצפן_בשלות_v6_דאטהסט.xlsx
+++ b/מצפן_בשלות_v6_דאטהסט.xlsx
@@ -2244,7 +2244,7 @@
       <c r="G25" s="7" t="inlineStr">
         <is>
           <t>להבין את הבעיה החברתית שאיתה אתם מתמודדים
-ללמוד על המוטבים ועל הסביבה שבה הם חיים
+להכיר את המוטבים ואת הצרכים שלהם
 לתכנן איך מפעילים את התכנית או השירות
 למדוד תוצאות ואימפקט
 לתכנן את שנת העבודה ולעקוב אחרי יעדים
@@ -3614,6 +3614,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
@@ -3697,6 +3698,7 @@
       <c r="D20" s="7" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr"/>
     </row>
+    <row r="21"/>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
@@ -3811,6 +3813,7 @@
       <c r="D27" s="13" t="n"/>
       <c r="E27" s="14" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
@@ -3956,6 +3959,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
@@ -5269,6 +5273,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
@@ -8189,10 +8194,10 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A113:A115"/>
+    <mergeCell ref="B116:B120"/>
+    <mergeCell ref="C15:C18"/>
     <mergeCell ref="A58:A59"/>
-    <mergeCell ref="C15:C18"/>
     <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B116:B120"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="A123:A124"/>
     <mergeCell ref="A129:A133"/>
